--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$59</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$60</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -793,7 +793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B8" s="10">
-        <f>B26</f>
+        <f>B27</f>
         <v/>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -869,7 +869,7 @@
         </is>
       </c>
       <c r="F8" s="8">
-        <f>B39-(B44+B45+B46)/12</f>
+        <f>B40-(B45+B46+B47)/12</f>
         <v/>
       </c>
     </row>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>B37</f>
+        <f>B38</f>
         <v/>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="F9" s="8">
-        <f>B50</f>
+        <f>B51</f>
         <v/>
       </c>
     </row>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B10" s="11">
-        <f>B39</f>
+        <f>B40</f>
         <v/>
       </c>
     </row>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B11" s="11">
-        <f>B50</f>
+        <f>B51</f>
         <v/>
       </c>
     </row>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>B55</f>
+        <f>B56</f>
         <v/>
       </c>
     </row>
@@ -1050,364 +1050,381 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Classe énergie (DPE)</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>annoncée par le vendeur — demander le diagnostic complet</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>HYPOTHÈSES — cellules jaunes à ajuster avec votre conseiller</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>Prix négocié retenu</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="n">
-        <v>390000</v>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>par défaut le prix affiché — un prix demandé se négocie</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
         <is>
-          <t>Frais d'acquisition (notaire, garanties)</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n">
-        <v>0.08</v>
+          <t>Prix négocié retenu</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="n">
+        <v>390000</v>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>par défaut le prix affiché — un prix demandé se négocie</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Frais d'acquisition (notaire, garanties)</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
-          <t>Taux du crédit (hors assurance)</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Durée du crédit (années)</t>
-        </is>
-      </c>
-      <c r="B30" s="21" t="n">
-        <v>20</v>
+          <t>Taux du crédit (hors assurance)</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n">
+        <v>0.0475</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>Taxe foncière (en mois de loyer par an)</t>
-        </is>
-      </c>
-      <c r="B31" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>à remplacer par le montant réel dès que connu</t>
-        </is>
+          <t>Durée du crédit (années)</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Provision entretien &amp; vacance (% du loyer)</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="n">
-        <v>0.05</v>
+          <t>Taxe foncière (en mois de loyer par an)</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>à remplacer par le montant réel dès que connu</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
+          <t>Provision entretien &amp; vacance (% du loyer)</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
           <t>Assurance propriétaire (PNO, €/an)</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n">
+      <c r="B34" s="18" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>PLAN DE FINANCEMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Coût d'acquisition total</t>
-        </is>
-      </c>
-      <c r="B36" s="17">
-        <f>B26*(1+B27)</f>
-        <v/>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>prix négocié + frais d'acquisition</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
         <is>
-          <t>Apport personnel</t>
+          <t>Coût d'acquisition total</t>
         </is>
       </c>
       <c r="B37" s="17">
-        <f>B36*B28</f>
-        <v/>
+        <f>B27*(1+B28)</f>
+        <v/>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>prix négocié + frais d'acquisition</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Montant emprunté</t>
+          <t>Apport personnel</t>
         </is>
       </c>
       <c r="B38" s="17">
-        <f>B36-B37</f>
+        <f>B37*B29</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
         <is>
-          <t>Mensualité du crédit</t>
-        </is>
-      </c>
-      <c r="B39" s="23">
-        <f>IFERROR(-PMT(B29/12,B30*12,B38),0)</f>
+          <t>Montant emprunté</t>
+        </is>
+      </c>
+      <c r="B39" s="17">
+        <f>B37-B38</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
+          <t>Mensualité du crédit</t>
+        </is>
+      </c>
+      <c r="B40" s="23">
+        <f>IFERROR(-PMT(B30/12,B31*12,B39),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
           <t>Service de la dette (annuel)</t>
         </is>
       </c>
-      <c r="B40" s="17">
-        <f>B39*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="B41" s="17">
+        <f>B40*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>EXPLOITATION ANNUELLE</t>
         </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
-        <is>
-          <t>Loyers annuels HT</t>
-        </is>
-      </c>
-      <c r="B43" s="17">
-        <f>IFERROR(B20*12,0)</f>
-        <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>− Taxe foncière</t>
+          <t>Loyers annuels HT</t>
         </is>
       </c>
       <c r="B44" s="17">
-        <f>-IFERROR(B20*B31,0)</f>
+        <f>IFERROR(B20*12,0)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
         <is>
-          <t>− Entretien &amp; vacance locative</t>
+          <t>− Taxe foncière</t>
         </is>
       </c>
       <c r="B45" s="17">
-        <f>-B43*B32</f>
+        <f>-IFERROR(B20*B32,0)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>− Assurance PNO</t>
+          <t>− Entretien &amp; vacance locative</t>
         </is>
       </c>
       <c r="B46" s="17">
-        <f>-B33</f>
+        <f>-B44*B33</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="14" t="inlineStr">
         <is>
-          <t>Revenu net avant crédit</t>
+          <t>− Assurance PNO</t>
         </is>
       </c>
       <c r="B47" s="17">
-        <f>B43+B44+B45+B46</f>
+        <f>-B34</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>− Remboursement du crédit</t>
+          <t>Revenu net avant crédit</t>
         </is>
       </c>
       <c r="B48" s="17">
-        <f>-B40</f>
+        <f>B44+B45+B46+B47</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
-          <t>Cash-flow annuel</t>
+          <t>− Remboursement du crédit</t>
         </is>
       </c>
       <c r="B49" s="17">
-        <f>B47-B40</f>
+        <f>-B41</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
+          <t>Cash-flow annuel</t>
+        </is>
+      </c>
+      <c r="B50" s="17">
+        <f>B48-B41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
           <t>Cash-flow mensuel</t>
         </is>
       </c>
-      <c r="B50" s="24">
-        <f>B49/12</f>
-        <v/>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
+      <c r="B51" s="24">
+        <f>B50/12</f>
+        <v/>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>positif : le bien se paie tout seul, loyer ≥ crédit + charges</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>LES RATIOS QUE REGARDE LE BANQUIER</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>Rendement brut</t>
-        </is>
-      </c>
-      <c r="B53" s="25">
-        <f>IFERROR(B43/B26,"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="19" t="inlineStr">
-        <is>
-          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Rendement net avant crédit</t>
+          <t>Rendement brut</t>
         </is>
       </c>
       <c r="B54" s="25">
-        <f>IFERROR(B47/B36,"")</f>
+        <f>IFERROR(B44/B27,"")</f>
         <v/>
       </c>
       <c r="C54" s="19" t="inlineStr">
         <is>
-          <t>après taxe foncière, entretien et assurance</t>
+          <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
-          <t>DSCR — couverture de la dette</t>
-        </is>
-      </c>
-      <c r="B55" s="26">
-        <f>IFERROR(B47/B40,"")</f>
+          <t>Rendement net avant crédit</t>
+        </is>
+      </c>
+      <c r="B55" s="25">
+        <f>IFERROR(B48/B37,"")</f>
         <v/>
       </c>
       <c r="C55" s="19" t="inlineStr">
         <is>
-          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
+          <t>après taxe foncière, entretien et assurance</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="14" t="inlineStr">
         <is>
-          <t>LTV — part financée par la banque</t>
-        </is>
-      </c>
-      <c r="B56" s="25">
-        <f>IFERROR(B38/B26,"")</f>
+          <t>DSCR — couverture de la dette</t>
+        </is>
+      </c>
+      <c r="B56" s="26">
+        <f>IFERROR(B48/B41,"")</f>
         <v/>
       </c>
       <c r="C56" s="19" t="inlineStr">
         <is>
-          <t>≤ 80 % est la zone de confort bancaire</t>
+          <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="14" t="inlineStr">
         <is>
-          <t>Effort d'épargne mensuel si négatif</t>
-        </is>
-      </c>
-      <c r="B57" s="23">
-        <f>MAX(0,-B49/12)</f>
-        <v/>
+          <t>LTV — part financée par la banque</t>
+        </is>
+      </c>
+      <c r="B57" s="25">
+        <f>IFERROR(B39/B27,"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>≤ 80 % est la zone de confort bancaire</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="inlineStr">
         <is>
+          <t>Effort d'épargne mensuel si négatif</t>
+        </is>
+      </c>
+      <c r="B58" s="23">
+        <f>MAX(0,-B50/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
           <t>Score de l'outil de veille</t>
         </is>
       </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>74/100</t>
-        </is>
-      </c>
-      <c r="C58" s="19" t="inlineStr">
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>75/100</t>
+        </is>
+      </c>
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>rendement, emplacement, prix vs marché, financement, fiscalité</t>
         </is>
@@ -1416,18 +1433,18 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A36:C36"/>
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A13:C14"/>
-    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A52:C52"/>
   </mergeCells>
-  <conditionalFormatting sqref="B49">
+  <conditionalFormatting sqref="B50">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1435,7 +1452,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B50">
+  <conditionalFormatting sqref="B51">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1443,7 +1460,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B55">
+  <conditionalFormatting sqref="B56">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.2</formula>
     </cfRule>
@@ -1520,7 +1537,7 @@
         </is>
       </c>
       <c r="G1">
-        <f>'Synthèse'!B30</f>
+        <f>'Synthèse'!B31</f>
         <v/>
       </c>
     </row>
@@ -1529,7 +1546,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="8">
-        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$38,"")</f>
+        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$39,"")</f>
         <v/>
       </c>
       <c r="C2" s="8">
@@ -1550,7 +1567,7 @@
         </is>
       </c>
       <c r="G2">
-        <f>'Synthèse'!B29</f>
+        <f>'Synthèse'!B30</f>
         <v/>
       </c>
     </row>
@@ -1575,7 +1592,7 @@
         <v/>
       </c>
       <c r="G3">
-        <f>'Synthèse'!B40</f>
+        <f>'Synthèse'!B41</f>
         <v/>
       </c>
     </row>
@@ -2302,7 +2319,7 @@
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>Décote sans explication visible dans l'annonce : possible bonne affaire — ou défaut caché (état, copropriété, bail) à vérifier sur place.</t>
+          <t>Décote lisible : des travaux sont signalés dans l'annonce.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 130 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +178 €/mois.</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>2391.67</v>
+        <v>2747</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>75/100</t>
+          <t>86/100</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +178 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 130 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>2747</v>
+        <v>2391.67</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>86/100</t>
+          <t>75/100</t>
         </is>
       </c>
       <c r="C59" s="19" t="inlineStr">

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), il reste environ 130 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), il reste environ 157 €/mois à financer en plus du loyer — marge de négociation ou apport supplémentaire à prévoir.</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         </is>
       </c>
       <c r="B30" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="31">

--- a/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
+++ b/docs/dossiers/dossier-paris-17e-75017-bd48367f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
